--- a/lab-standards/BMET-lab-standard.xlsx
+++ b/lab-standards/BMET-lab-standard.xlsx
@@ -128,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -161,6 +161,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8620,10 +8626,6 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -8633,13 +8635,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Classroom cum workshop – 500 - 600 sft (50-55 sqm)</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12" t="n"/>
+          <t>Classroom – 350 sft (33 sqm)
+lab size – 500 sft (47 sqm)
+OR
+Classroom cum workshop – 500 sft (47 sqm)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -8698,13 +8699,13 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5-i3 6 gen or AMD Ryzen 5), Ram: minimum 8 - 16 GB, Graphic Card: dedicated GPU 2GB, High Speed Internet (Minimum 10 Mbps), Graphic Design Software 
-(Photoshop CC, Illustrator CC, CorelDraw)</t>
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+(Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -8723,7 +8724,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -8747,7 +8748,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -8771,7 +8772,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -8795,7 +8796,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -8819,7 +8820,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -8843,7 +8844,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -8867,16 +8868,16 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Air-conditioning (suited with workshop lab size)</t>
+          <t>Ergonomic chairs and desks (Plastic chairs/stool not acceptable)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>0</v>
@@ -8890,96 +8891,80 @@
       </c>
       <c r="G23" s="9" t="n"/>
     </row>
-    <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Ergonomic chairs and desks (Plastic chairs/stool not acceptable)</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="9">
-        <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="9" t="n"/>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="15">
+        <f>SUM(E16:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="15">
+        <f>SUM(F16:F23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Sum</t>
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Score out of 100</t>
         </is>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="10">
-        <f>SUM(E16:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="10">
-        <f>SUM(F16:F24)</f>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="15">
+        <f>F24/E24*100</f>
         <v/>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Score out of 100</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="10">
-        <f>F25/E25*100</f>
-        <v/>
-      </c>
-      <c r="G26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="9.75" customHeight="1"/>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="26" ht="9.75" customHeight="1"/>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
-        <f>F26*30/100</f>
-        <v/>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="15">
+        <f>F25*30/100</f>
+        <v/>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the lab should be air-conditioned. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:D24"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lab-standards/BMET-lab-standard.xlsx
+++ b/lab-standards/BMET-lab-standard.xlsx
@@ -671,7 +671,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -695,7 +695,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -719,7 +719,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -743,7 +743,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -767,7 +767,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -791,7 +791,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -815,7 +815,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -839,7 +839,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -863,7 +863,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -887,7 +887,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -911,7 +911,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -935,7 +935,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -959,7 +959,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -983,7 +983,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -1007,7 +1007,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1031,7 +1031,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1055,7 +1055,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1079,7 +1079,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1103,7 +1103,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1127,7 +1127,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -1151,7 +1151,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -1175,7 +1175,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -1223,7 +1223,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1231,18 +1231,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="10">
+      <c r="E39" s="15">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="15">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1251,7 +1251,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="10">
+      <c r="F40" s="15">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1268,11 +1268,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="10">
+      <c r="F42" s="15">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1439,7 +1439,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1463,7 +1463,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1511,7 +1511,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1535,7 +1535,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1559,7 +1559,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1583,7 +1583,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1607,7 +1607,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1631,7 +1631,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1655,7 +1655,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -1679,7 +1679,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -1703,7 +1703,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1727,7 +1727,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1751,7 +1751,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -1775,7 +1775,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1799,7 +1799,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1823,7 +1823,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1847,7 +1847,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1871,7 +1871,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1895,7 +1895,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1903,18 +1903,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1923,7 +1923,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1931,7 +1931,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1940,11 +1940,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2109,7 +2109,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2133,7 +2133,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2157,7 +2157,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2181,7 +2181,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2205,7 +2205,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2229,7 +2229,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2253,7 +2253,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2277,7 +2277,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2301,7 +2301,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2325,7 +2325,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2349,7 +2349,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2373,7 +2373,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2397,7 +2397,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2421,7 +2421,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2445,7 +2445,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2469,7 +2469,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2493,7 +2493,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2517,7 +2517,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2541,7 +2541,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2565,7 +2565,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -2589,7 +2589,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -2613,7 +2613,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -2637,7 +2637,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -2661,7 +2661,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39" ht="14.15" customHeight="1">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="14" t="n">
         <v>24</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -2685,7 +2685,7 @@
       <c r="G39" s="9" t="n"/>
     </row>
     <row r="40" ht="14.15" customHeight="1">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="14" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -2709,7 +2709,7 @@
       <c r="G40" s="9" t="n"/>
     </row>
     <row r="41" ht="14.15" customHeight="1">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="14" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -2733,7 +2733,7 @@
       <c r="G41" s="9" t="n"/>
     </row>
     <row r="42" ht="14.15" customHeight="1">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="14" t="n">
         <v>27</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -2757,7 +2757,7 @@
       <c r="G42" s="9" t="n"/>
     </row>
     <row r="43" ht="14.15" customHeight="1">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="14" t="n">
         <v>28</v>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -2781,7 +2781,7 @@
       <c r="G43" s="9" t="n"/>
     </row>
     <row r="44" ht="14.15" customHeight="1">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="14" t="n">
         <v>29</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -2805,7 +2805,7 @@
       <c r="G44" s="9" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2813,18 +2813,18 @@
       <c r="B45" s="11" t="n"/>
       <c r="C45" s="11" t="n"/>
       <c r="D45" s="12" t="n"/>
-      <c r="E45" s="10">
+      <c r="E45" s="15">
         <f>SUM(E16:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="15">
         <f>SUM(F16:F44)</f>
         <v/>
       </c>
       <c r="G45" s="13" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2833,7 +2833,7 @@
       <c r="C46" s="11" t="n"/>
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="12" t="n"/>
-      <c r="F46" s="10">
+      <c r="F46" s="15">
         <f>F45/E45*100</f>
         <v/>
       </c>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="47" ht="9.75" customHeight="1"/>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2850,11 +2850,11 @@
       <c r="C48" s="11" t="n"/>
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="12" t="n"/>
-      <c r="F48" s="10">
+      <c r="F48" s="15">
         <f>F46*30/100</f>
         <v/>
       </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="G48" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3019,7 +3019,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3043,7 +3043,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3067,7 +3067,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3091,7 +3091,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3115,7 +3115,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3139,7 +3139,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3163,7 +3163,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3187,7 +3187,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3211,7 +3211,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3235,7 +3235,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -3259,7 +3259,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3283,7 +3283,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3307,7 +3307,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3331,7 +3331,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3355,7 +3355,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3379,7 +3379,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3403,7 +3403,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3427,7 +3427,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3451,7 +3451,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -3475,7 +3475,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3483,18 +3483,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3503,7 +3503,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -3511,7 +3511,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3520,11 +3520,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3690,7 +3690,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3714,7 +3714,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3762,7 +3762,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3786,7 +3786,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3810,7 +3810,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3834,7 +3834,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3858,7 +3858,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3882,7 +3882,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3906,7 +3906,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3954,7 +3954,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3978,7 +3978,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -4026,7 +4026,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -4050,7 +4050,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -4074,7 +4074,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -4098,7 +4098,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -4122,7 +4122,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4146,7 +4146,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -4194,7 +4194,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -4218,7 +4218,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -4242,7 +4242,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -4250,18 +4250,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="10">
+      <c r="E39" s="15">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="15">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -4270,7 +4270,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="10">
+      <c r="F40" s="15">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -4278,7 +4278,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -4287,11 +4287,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="10">
+      <c r="F42" s="15">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -4457,7 +4457,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -4481,7 +4481,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4505,7 +4505,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4529,7 +4529,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -4553,7 +4553,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -4577,7 +4577,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -4601,7 +4601,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4625,7 +4625,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4649,7 +4649,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -4673,7 +4673,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -4697,7 +4697,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -4721,7 +4721,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -4745,7 +4745,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -4769,7 +4769,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -4793,7 +4793,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -4817,7 +4817,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -4841,7 +4841,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -4865,7 +4865,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -4889,7 +4889,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4913,7 +4913,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -4921,18 +4921,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -4941,7 +4941,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -4949,7 +4949,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -4958,11 +4958,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -5127,7 +5127,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -5151,7 +5151,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -5175,7 +5175,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -5199,7 +5199,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -5223,7 +5223,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -5247,7 +5247,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -5271,7 +5271,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -5295,7 +5295,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -5319,7 +5319,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -5343,7 +5343,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -5367,7 +5367,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -5391,7 +5391,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -5415,7 +5415,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -5439,7 +5439,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -5463,7 +5463,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -5487,7 +5487,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -5511,7 +5511,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -5535,7 +5535,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -5559,7 +5559,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -5567,18 +5567,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="10">
+      <c r="E34" s="15">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="15">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -5587,7 +5587,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -5604,11 +5604,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="10">
+      <c r="F37" s="15">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -5775,7 +5775,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -5799,7 +5799,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -5823,7 +5823,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -5847,7 +5847,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -5871,7 +5871,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -5895,7 +5895,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -5919,7 +5919,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -5943,7 +5943,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -5967,7 +5967,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -5991,7 +5991,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -6015,7 +6015,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -6039,7 +6039,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -6063,7 +6063,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -6087,7 +6087,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -6095,18 +6095,18 @@
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="12" t="n"/>
-      <c r="E29" s="10">
+      <c r="E29" s="15">
         <f>SUM(E16:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="15">
         <f>SUM(F16:F28)</f>
         <v/>
       </c>
       <c r="G29" s="13" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -6115,7 +6115,7 @@
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10">
+      <c r="F30" s="15">
         <f>F29/E29*100</f>
         <v/>
       </c>
@@ -6123,7 +6123,7 @@
     </row>
     <row r="31" ht="9.75" customHeight="1"/>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -6132,11 +6132,11 @@
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="12" t="n"/>
-      <c r="F32" s="10">
+      <c r="F32" s="15">
         <f>F30*30/100</f>
         <v/>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -6302,7 +6302,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -6326,7 +6326,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -6350,7 +6350,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -6374,7 +6374,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -6398,7 +6398,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -6422,7 +6422,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -6446,7 +6446,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -6470,7 +6470,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -6590,18 +6590,18 @@
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="12" t="n"/>
-      <c r="E27" s="10">
+      <c r="E27" s="15">
         <f>SUM(E16:E26)</f>
         <v/>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="15">
         <f>SUM(F16:F26)</f>
         <v/>
       </c>
       <c r="G27" s="13" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -6610,7 +6610,7 @@
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
+      <c r="F28" s="15">
         <f>F27/E27*100</f>
         <v/>
       </c>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="29" ht="9.75" customHeight="1"/>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -6627,11 +6627,11 @@
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10">
+      <c r="F30" s="15">
         <f>F28*30/100</f>
         <v/>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -6797,7 +6797,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -7421,18 +7421,18 @@
       <c r="B38" s="11" t="n"/>
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="12" t="n"/>
-      <c r="E38" s="10">
+      <c r="E38" s="15">
         <f>SUM(E16:E37)</f>
         <v/>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>SUM(F16:F37)</f>
         <v/>
       </c>
       <c r="G38" s="13" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -7441,7 +7441,7 @@
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="12" t="n"/>
-      <c r="F39" s="10">
+      <c r="F39" s="15">
         <f>F38/E38*100</f>
         <v/>
       </c>
@@ -7449,7 +7449,7 @@
     </row>
     <row r="40" ht="9.75" customHeight="1"/>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -7458,11 +7458,11 @@
       <c r="C41" s="11" t="n"/>
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="12" t="n"/>
-      <c r="F41" s="10">
+      <c r="F41" s="15">
         <f>F39*30/100</f>
         <v/>
       </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="G41" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -7627,7 +7627,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -7651,7 +7651,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -7675,7 +7675,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -7699,7 +7699,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -7723,7 +7723,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -7747,7 +7747,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -7771,7 +7771,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -7795,7 +7795,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -7819,7 +7819,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -7843,7 +7843,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -7867,7 +7867,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -7891,7 +7891,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -7915,7 +7915,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -7939,7 +7939,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -7963,7 +7963,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -7987,7 +7987,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -8011,7 +8011,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -8035,7 +8035,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -8059,7 +8059,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -8083,7 +8083,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -8107,7 +8107,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -8131,7 +8131,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -8155,7 +8155,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -8179,7 +8179,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39" ht="14.15" customHeight="1">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="14" t="n">
         <v>24</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -8203,7 +8203,7 @@
       <c r="G39" s="9" t="n"/>
     </row>
     <row r="40" ht="14.15" customHeight="1">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="14" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -8227,7 +8227,7 @@
       <c r="G40" s="9" t="n"/>
     </row>
     <row r="41" ht="14.15" customHeight="1">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="14" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -8251,7 +8251,7 @@
       <c r="G41" s="9" t="n"/>
     </row>
     <row r="42" ht="14.15" customHeight="1">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="14" t="n">
         <v>27</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -8275,7 +8275,7 @@
       <c r="G42" s="9" t="n"/>
     </row>
     <row r="43" ht="14.15" customHeight="1">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="14" t="n">
         <v>28</v>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -8299,7 +8299,7 @@
       <c r="G43" s="9" t="n"/>
     </row>
     <row r="44" ht="14.15" customHeight="1">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="14" t="n">
         <v>29</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -8323,7 +8323,7 @@
       <c r="G44" s="9" t="n"/>
     </row>
     <row r="45" ht="14.15" customHeight="1">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="14" t="n">
         <v>30</v>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -8347,7 +8347,7 @@
       <c r="G45" s="9" t="n"/>
     </row>
     <row r="46" ht="14.15" customHeight="1">
-      <c r="A46" s="7" t="n">
+      <c r="A46" s="14" t="n">
         <v>31</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -8371,7 +8371,7 @@
       <c r="G46" s="9" t="n"/>
     </row>
     <row r="47" ht="14.15" customHeight="1">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="14" t="n">
         <v>32</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -8395,7 +8395,7 @@
       <c r="G47" s="9" t="n"/>
     </row>
     <row r="48" ht="14.15" customHeight="1">
-      <c r="A48" s="7" t="n">
+      <c r="A48" s="14" t="n">
         <v>33</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -8419,7 +8419,7 @@
       <c r="G48" s="9" t="n"/>
     </row>
     <row r="49" ht="14.15" customHeight="1">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="14" t="n">
         <v>34</v>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -8443,7 +8443,7 @@
       <c r="G49" s="9" t="n"/>
     </row>
     <row r="50" ht="14.15" customHeight="1">
-      <c r="A50" s="7" t="n">
+      <c r="A50" s="14" t="n">
         <v>35</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -8467,7 +8467,7 @@
       <c r="G50" s="9" t="n"/>
     </row>
     <row r="51" ht="14.15" customHeight="1">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="14" t="n">
         <v>36</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -8491,7 +8491,7 @@
       <c r="G51" s="9" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -8499,18 +8499,18 @@
       <c r="B52" s="11" t="n"/>
       <c r="C52" s="11" t="n"/>
       <c r="D52" s="12" t="n"/>
-      <c r="E52" s="10">
+      <c r="E52" s="15">
         <f>SUM(E16:E51)</f>
         <v/>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="15">
         <f>SUM(F16:F51)</f>
         <v/>
       </c>
       <c r="G52" s="13" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -8519,7 +8519,7 @@
       <c r="C53" s="11" t="n"/>
       <c r="D53" s="11" t="n"/>
       <c r="E53" s="12" t="n"/>
-      <c r="F53" s="10">
+      <c r="F53" s="15">
         <f>F52/E52*100</f>
         <v/>
       </c>
@@ -8527,7 +8527,7 @@
     </row>
     <row r="54" ht="9.75" customHeight="1"/>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -8536,11 +8536,11 @@
       <c r="C55" s="11" t="n"/>
       <c r="D55" s="11" t="n"/>
       <c r="E55" s="12" t="n"/>
-      <c r="F55" s="10">
+      <c r="F55" s="15">
         <f>F53*30/100</f>
         <v/>
       </c>
-      <c r="G55" s="10" t="inlineStr">
+      <c r="G55" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -8586,6 +8586,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -8608,6 +8609,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -8626,6 +8628,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -8641,7 +8647,13 @@
 Classroom cum workshop – 500 sft (47 sqm)</t>
         </is>
       </c>
-    </row>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -8649,6 +8661,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -8660,6 +8673,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -8704,7 +8718,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
 (Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>
@@ -9115,7 +9129,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -9139,7 +9153,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -9163,7 +9177,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -9187,7 +9201,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -9211,7 +9225,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -9235,7 +9249,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -9259,7 +9273,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -9283,7 +9297,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -9307,7 +9321,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -9331,7 +9345,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -9355,7 +9369,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -9379,7 +9393,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -9403,7 +9417,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -9427,7 +9441,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -9451,7 +9465,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -9475,7 +9489,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -9499,7 +9513,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -9507,18 +9521,18 @@
       <c r="B32" s="11" t="n"/>
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="12" t="n"/>
-      <c r="E32" s="10">
+      <c r="E32" s="15">
         <f>SUM(E16:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="15">
         <f>SUM(F16:F31)</f>
         <v/>
       </c>
       <c r="G32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -9527,7 +9541,7 @@
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="12" t="n"/>
-      <c r="F33" s="10">
+      <c r="F33" s="15">
         <f>F32/E32*100</f>
         <v/>
       </c>
@@ -9535,7 +9549,7 @@
     </row>
     <row r="34" ht="9.75" customHeight="1"/>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -9544,11 +9558,11 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>F33*30/100</f>
         <v/>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G35" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -9714,7 +9728,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -9738,7 +9752,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -9762,7 +9776,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -9786,7 +9800,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -9810,7 +9824,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -9834,7 +9848,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -9858,7 +9872,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -9882,7 +9896,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -9906,7 +9920,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -9930,7 +9944,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -9954,7 +9968,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -9978,7 +9992,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -10002,7 +10016,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -10026,7 +10040,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -10050,7 +10064,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -10074,7 +10088,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -10082,18 +10096,18 @@
       <c r="B31" s="11" t="n"/>
       <c r="C31" s="11" t="n"/>
       <c r="D31" s="12" t="n"/>
-      <c r="E31" s="10">
+      <c r="E31" s="15">
         <f>SUM(E16:E30)</f>
         <v/>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="15">
         <f>SUM(F16:F30)</f>
         <v/>
       </c>
       <c r="G31" s="13" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -10102,7 +10116,7 @@
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="12" t="n"/>
-      <c r="F32" s="10">
+      <c r="F32" s="15">
         <f>F31/E31*100</f>
         <v/>
       </c>
@@ -10110,7 +10124,7 @@
     </row>
     <row r="33" ht="9.75" customHeight="1"/>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -10119,11 +10133,11 @@
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="12" t="n"/>
-      <c r="F34" s="10">
+      <c r="F34" s="15">
         <f>F32*30/100</f>
         <v/>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -10290,7 +10304,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -10314,7 +10328,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -10338,7 +10352,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -10362,7 +10376,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -10386,7 +10400,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -10410,7 +10424,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -10434,7 +10448,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -10458,7 +10472,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -10482,7 +10496,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -10506,7 +10520,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -10530,7 +10544,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -10554,7 +10568,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -10578,7 +10592,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -10602,7 +10616,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -10626,7 +10640,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -10650,7 +10664,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -10674,7 +10688,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -10698,7 +10712,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -10706,18 +10720,18 @@
       <c r="B33" s="11" t="n"/>
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="12" t="n"/>
-      <c r="E33" s="10">
+      <c r="E33" s="15">
         <f>SUM(E16:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="15">
         <f>SUM(F16:F32)</f>
         <v/>
       </c>
       <c r="G33" s="13" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -10726,7 +10740,7 @@
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="12" t="n"/>
-      <c r="F34" s="10">
+      <c r="F34" s="15">
         <f>F33/E33*100</f>
         <v/>
       </c>
@@ -10734,7 +10748,7 @@
     </row>
     <row r="35" ht="9.75" customHeight="1"/>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -10743,11 +10757,11 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F34*30/100</f>
         <v/>
       </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="G36" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -10914,7 +10928,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -10938,7 +10952,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -10962,7 +10976,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -10986,7 +11000,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -11010,7 +11024,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -11034,7 +11048,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -11058,7 +11072,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -11082,7 +11096,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -11106,7 +11120,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -11130,7 +11144,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -11154,7 +11168,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -11178,7 +11192,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -11202,7 +11216,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -11226,7 +11240,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -11250,7 +11264,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -11258,18 +11272,18 @@
       <c r="B30" s="11" t="n"/>
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="12" t="n"/>
-      <c r="E30" s="10">
+      <c r="E30" s="15">
         <f>SUM(E16:E29)</f>
         <v/>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="15">
         <f>SUM(F16:F29)</f>
         <v/>
       </c>
       <c r="G30" s="13" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -11278,7 +11292,7 @@
       <c r="C31" s="11" t="n"/>
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="12" t="n"/>
-      <c r="F31" s="10">
+      <c r="F31" s="15">
         <f>F30/E30*100</f>
         <v/>
       </c>
@@ -11286,7 +11300,7 @@
     </row>
     <row r="32" ht="9.75" customHeight="1"/>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -11295,11 +11309,11 @@
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="12" t="n"/>
-      <c r="F33" s="10">
+      <c r="F33" s="15">
         <f>F31*30/100</f>
         <v/>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -11466,7 +11480,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -11490,7 +11504,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -11514,7 +11528,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -11538,7 +11552,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -11562,7 +11576,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -11586,7 +11600,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -11610,7 +11624,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -11634,7 +11648,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -11658,7 +11672,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -11682,7 +11696,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -11706,7 +11720,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -11730,7 +11744,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -11754,7 +11768,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -11778,7 +11792,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -11802,7 +11816,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -11826,7 +11840,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -11850,7 +11864,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -11874,7 +11888,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -11898,7 +11912,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -11922,7 +11936,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -11930,18 +11944,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -11950,7 +11964,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -11958,7 +11972,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -11967,11 +11981,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -12137,7 +12151,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -12161,7 +12175,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -12185,7 +12199,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -12209,7 +12223,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -12233,7 +12247,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -12257,7 +12271,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -12281,7 +12295,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -12305,7 +12319,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -12329,7 +12343,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -12353,7 +12367,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -12377,7 +12391,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -12401,7 +12415,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -12425,7 +12439,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -12449,7 +12463,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -12473,7 +12487,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -12497,7 +12511,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -12521,7 +12535,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -12529,18 +12543,18 @@
       <c r="B32" s="11" t="n"/>
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="12" t="n"/>
-      <c r="E32" s="10">
+      <c r="E32" s="15">
         <f>SUM(E16:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="15">
         <f>SUM(F16:F31)</f>
         <v/>
       </c>
       <c r="G32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -12549,7 +12563,7 @@
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="12" t="n"/>
-      <c r="F33" s="10">
+      <c r="F33" s="15">
         <f>F32/E32*100</f>
         <v/>
       </c>
@@ -12557,7 +12571,7 @@
     </row>
     <row r="34" ht="9.75" customHeight="1"/>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -12566,11 +12580,11 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>F33*30/100</f>
         <v/>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G35" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -12736,7 +12750,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -12760,7 +12774,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -12784,7 +12798,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -12808,7 +12822,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -12832,7 +12846,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -12856,7 +12870,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -12880,7 +12894,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -12904,7 +12918,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -12928,7 +12942,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -12952,7 +12966,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -12976,7 +12990,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -13000,7 +13014,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -13024,7 +13038,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -13048,7 +13062,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -13072,7 +13086,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -13096,7 +13110,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -13120,7 +13134,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -13144,7 +13158,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -13168,7 +13182,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -13176,18 +13190,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="10">
+      <c r="E34" s="15">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="15">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -13196,7 +13210,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -13204,7 +13218,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -13213,11 +13227,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="10">
+      <c r="F37" s="15">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -13385,7 +13399,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -13409,7 +13423,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -13433,7 +13447,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -13457,7 +13471,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -13481,7 +13495,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -13505,7 +13519,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -13529,7 +13543,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -13553,7 +13567,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -13577,7 +13591,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -13601,7 +13615,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -13625,7 +13639,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -13653,7 +13667,7 @@
       </c>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -13677,7 +13691,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -13701,7 +13715,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -13709,18 +13723,18 @@
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="12" t="n"/>
-      <c r="E29" s="10">
+      <c r="E29" s="15">
         <f>SUM(E16:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="15">
         <f>SUM(F16:F28)</f>
         <v/>
       </c>
       <c r="G29" s="13" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -13729,7 +13743,7 @@
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10">
+      <c r="F30" s="15">
         <f>F29/E29*100</f>
         <v/>
       </c>
@@ -13737,7 +13751,7 @@
     </row>
     <row r="31" ht="9.75" customHeight="1"/>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -13746,11 +13760,11 @@
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="12" t="n"/>
-      <c r="F32" s="10">
+      <c r="F32" s="15">
         <f>F30*30/100</f>
         <v/>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -13916,7 +13930,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -13940,7 +13954,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -13964,7 +13978,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -13988,7 +14002,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -14012,7 +14026,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -14036,7 +14050,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -14060,7 +14074,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -14084,7 +14098,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -14108,7 +14122,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -14132,7 +14146,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -14156,7 +14170,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -14180,7 +14194,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -14204,7 +14218,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -14228,7 +14242,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -14252,7 +14266,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -14276,7 +14290,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -14300,7 +14314,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -14324,7 +14338,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -14348,7 +14362,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -14372,7 +14386,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -14396,7 +14410,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -14420,7 +14434,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -14444,7 +14458,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -14468,7 +14482,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -14476,18 +14490,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="10">
+      <c r="E39" s="15">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="15">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -14496,7 +14510,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="10">
+      <c r="F40" s="15">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -14504,7 +14518,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -14513,11 +14527,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="10">
+      <c r="F42" s="15">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -14682,7 +14696,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -14706,7 +14720,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -14730,7 +14744,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -14754,7 +14768,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -14778,7 +14792,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -14802,7 +14816,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -14826,7 +14840,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -14850,7 +14864,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -14874,7 +14888,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -14898,7 +14912,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -14922,7 +14936,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -14946,7 +14960,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -14970,7 +14984,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -14994,7 +15008,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -15018,7 +15032,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -15042,7 +15056,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -15066,7 +15080,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -15090,7 +15104,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -15114,7 +15128,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -15138,7 +15152,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -15162,7 +15176,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -15186,7 +15200,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -15210,7 +15224,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -15234,7 +15248,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39" ht="14.15" customHeight="1">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="14" t="n">
         <v>24</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -15258,7 +15272,7 @@
       <c r="G39" s="9" t="n"/>
     </row>
     <row r="40" ht="14.15" customHeight="1">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="14" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -15282,7 +15296,7 @@
       <c r="G40" s="9" t="n"/>
     </row>
     <row r="41" ht="14.15" customHeight="1">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="14" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -15306,7 +15320,7 @@
       <c r="G41" s="9" t="n"/>
     </row>
     <row r="42" ht="14.15" customHeight="1">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="14" t="n">
         <v>27</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -15330,7 +15344,7 @@
       <c r="G42" s="9" t="n"/>
     </row>
     <row r="43" ht="14.15" customHeight="1">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="14" t="n">
         <v>28</v>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -15354,7 +15368,7 @@
       <c r="G43" s="9" t="n"/>
     </row>
     <row r="44" ht="14.15" customHeight="1">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="14" t="n">
         <v>29</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -15378,7 +15392,7 @@
       <c r="G44" s="9" t="n"/>
     </row>
     <row r="45" ht="14.15" customHeight="1">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="14" t="n">
         <v>30</v>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -15402,7 +15416,7 @@
       <c r="G45" s="9" t="n"/>
     </row>
     <row r="46" ht="14.15" customHeight="1">
-      <c r="A46" s="7" t="n">
+      <c r="A46" s="14" t="n">
         <v>31</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -15426,7 +15440,7 @@
       <c r="G46" s="9" t="n"/>
     </row>
     <row r="47" ht="14.15" customHeight="1">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="14" t="n">
         <v>32</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -15450,7 +15464,7 @@
       <c r="G47" s="9" t="n"/>
     </row>
     <row r="48" ht="14.15" customHeight="1">
-      <c r="A48" s="7" t="n">
+      <c r="A48" s="14" t="n">
         <v>33</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -15474,7 +15488,7 @@
       <c r="G48" s="9" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -15482,18 +15496,18 @@
       <c r="B49" s="11" t="n"/>
       <c r="C49" s="11" t="n"/>
       <c r="D49" s="12" t="n"/>
-      <c r="E49" s="10">
+      <c r="E49" s="15">
         <f>SUM(E16:E48)</f>
         <v/>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="15">
         <f>SUM(F16:F48)</f>
         <v/>
       </c>
       <c r="G49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -15502,7 +15516,7 @@
       <c r="C50" s="11" t="n"/>
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="12" t="n"/>
-      <c r="F50" s="10">
+      <c r="F50" s="15">
         <f>F49/E49*100</f>
         <v/>
       </c>
@@ -15510,7 +15524,7 @@
     </row>
     <row r="51" ht="9.75" customHeight="1"/>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -15519,11 +15533,11 @@
       <c r="C52" s="11" t="n"/>
       <c r="D52" s="11" t="n"/>
       <c r="E52" s="12" t="n"/>
-      <c r="F52" s="10">
+      <c r="F52" s="15">
         <f>F50*30/100</f>
         <v/>
       </c>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="G52" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -15688,7 +15702,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -15712,7 +15726,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -15736,7 +15750,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -15764,7 +15778,7 @@
       </c>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -15800,7 +15814,7 @@
       </c>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -15824,7 +15838,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -15848,7 +15862,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -15876,7 +15890,7 @@
       </c>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -15900,7 +15914,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -15924,7 +15938,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -15948,7 +15962,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -15972,7 +15986,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -15996,7 +16010,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -16020,7 +16034,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -16044,7 +16058,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -16072,7 +16086,7 @@
       </c>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -16100,7 +16114,7 @@
       </c>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -16124,7 +16138,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -16148,7 +16162,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -16172,7 +16186,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -16196,7 +16210,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -16220,7 +16234,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -16244,7 +16258,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -16268,7 +16282,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39" ht="14.15" customHeight="1">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="14" t="n">
         <v>24</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -16292,7 +16306,7 @@
       <c r="G39" s="9" t="n"/>
     </row>
     <row r="40" ht="14.15" customHeight="1">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="14" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -16316,7 +16330,7 @@
       <c r="G40" s="9" t="n"/>
     </row>
     <row r="41" ht="14.15" customHeight="1">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="14" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -16340,7 +16354,7 @@
       <c r="G41" s="9" t="n"/>
     </row>
     <row r="42" ht="14.15" customHeight="1">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="14" t="n">
         <v>27</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -16364,7 +16378,7 @@
       <c r="G42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -16372,18 +16386,18 @@
       <c r="B43" s="11" t="n"/>
       <c r="C43" s="11" t="n"/>
       <c r="D43" s="12" t="n"/>
-      <c r="E43" s="10">
+      <c r="E43" s="15">
         <f>SUM(E16:E42)</f>
         <v/>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="15">
         <f>SUM(F16:F42)</f>
         <v/>
       </c>
       <c r="G43" s="13" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -16392,7 +16406,7 @@
       <c r="C44" s="11" t="n"/>
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="12" t="n"/>
-      <c r="F44" s="10">
+      <c r="F44" s="15">
         <f>F43/E43*100</f>
         <v/>
       </c>
@@ -16400,7 +16414,7 @@
     </row>
     <row r="45" ht="9.75" customHeight="1"/>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -16409,11 +16423,11 @@
       <c r="C46" s="11" t="n"/>
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="12" t="n"/>
-      <c r="F46" s="10">
+      <c r="F46" s="15">
         <f>F44*30/100</f>
         <v/>
       </c>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="G46" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -16579,7 +16593,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -16603,7 +16617,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -16627,7 +16641,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -16651,7 +16665,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -16675,7 +16689,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -16699,7 +16713,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -16723,7 +16737,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -16751,7 +16765,7 @@
       </c>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -16779,7 +16793,7 @@
       </c>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -16807,7 +16821,7 @@
       </c>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -16831,7 +16845,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -16855,7 +16869,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -16879,7 +16893,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -16903,7 +16917,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -16927,7 +16941,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -16951,7 +16965,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -16975,7 +16989,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -16999,7 +17013,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -17023,7 +17037,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -17047,7 +17061,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -17071,7 +17085,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -17095,7 +17109,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -17119,7 +17133,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -17143,7 +17157,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39" ht="14.15" customHeight="1">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="14" t="n">
         <v>24</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -17167,7 +17181,7 @@
       <c r="G39" s="9" t="n"/>
     </row>
     <row r="40" ht="14.15" customHeight="1">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="14" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -17191,7 +17205,7 @@
       <c r="G40" s="9" t="n"/>
     </row>
     <row r="41" ht="14.15" customHeight="1">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="14" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -17219,7 +17233,7 @@
       </c>
     </row>
     <row r="42" ht="14.15" customHeight="1">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="14" t="n">
         <v>27</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -17243,7 +17257,7 @@
       <c r="G42" s="9" t="n"/>
     </row>
     <row r="43" ht="14.15" customHeight="1">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="14" t="n">
         <v>28</v>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -17267,7 +17281,7 @@
       <c r="G43" s="9" t="n"/>
     </row>
     <row r="44" ht="14.15" customHeight="1">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="14" t="n">
         <v>29</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -17291,7 +17305,7 @@
       <c r="G44" s="9" t="n"/>
     </row>
     <row r="45" ht="14.15" customHeight="1">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="14" t="n">
         <v>30</v>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -17315,7 +17329,7 @@
       <c r="G45" s="9" t="n"/>
     </row>
     <row r="46" ht="14.15" customHeight="1">
-      <c r="A46" s="7" t="n">
+      <c r="A46" s="14" t="n">
         <v>31</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -17339,7 +17353,7 @@
       <c r="G46" s="9" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -17347,18 +17361,18 @@
       <c r="B47" s="11" t="n"/>
       <c r="C47" s="11" t="n"/>
       <c r="D47" s="12" t="n"/>
-      <c r="E47" s="10">
+      <c r="E47" s="15">
         <f>SUM(E16:E46)</f>
         <v/>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="15">
         <f>SUM(F16:F46)</f>
         <v/>
       </c>
       <c r="G47" s="13" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -17367,7 +17381,7 @@
       <c r="C48" s="11" t="n"/>
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="12" t="n"/>
-      <c r="F48" s="10">
+      <c r="F48" s="15">
         <f>F47/E47*100</f>
         <v/>
       </c>
@@ -17375,7 +17389,7 @@
     </row>
     <row r="49" ht="9.75" customHeight="1"/>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -17384,11 +17398,11 @@
       <c r="C50" s="11" t="n"/>
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="12" t="n"/>
-      <c r="F50" s="10">
+      <c r="F50" s="15">
         <f>F48*30/100</f>
         <v/>
       </c>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="G50" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -17554,7 +17568,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -17578,7 +17592,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -17602,7 +17616,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -17626,7 +17640,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -17650,7 +17664,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -17674,7 +17688,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -17698,7 +17712,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -17722,7 +17736,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -17746,7 +17760,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -17770,7 +17784,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -17794,7 +17808,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -17818,7 +17832,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -17842,7 +17856,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -17866,7 +17880,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -17874,18 +17888,18 @@
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="12" t="n"/>
-      <c r="E29" s="10">
+      <c r="E29" s="15">
         <f>SUM(E16:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="15">
         <f>SUM(F16:F28)</f>
         <v/>
       </c>
       <c r="G29" s="13" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -17894,7 +17908,7 @@
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10">
+      <c r="F30" s="15">
         <f>F29/E29*100</f>
         <v/>
       </c>
@@ -17902,7 +17916,7 @@
     </row>
     <row r="31" ht="9.75" customHeight="1"/>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -17911,11 +17925,11 @@
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="12" t="n"/>
-      <c r="F32" s="10">
+      <c r="F32" s="15">
         <f>F30*30/100</f>
         <v/>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -18079,7 +18093,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -18103,7 +18117,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -18127,7 +18141,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -18151,7 +18165,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -18175,7 +18189,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -18199,7 +18213,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -18223,7 +18237,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -18247,7 +18261,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -18271,7 +18285,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -18295,7 +18309,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -18319,7 +18333,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -18343,7 +18357,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -18367,7 +18381,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -18391,7 +18405,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -18415,7 +18429,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -18439,7 +18453,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -18463,7 +18477,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -18487,7 +18501,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -18511,7 +18525,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -18535,7 +18549,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -18559,7 +18573,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -18583,7 +18597,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -18607,7 +18621,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -18631,7 +18645,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39" ht="14.15" customHeight="1">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="14" t="n">
         <v>24</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -18655,7 +18669,7 @@
       <c r="G39" s="9" t="n"/>
     </row>
     <row r="40" ht="14.15" customHeight="1">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="14" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -18679,7 +18693,7 @@
       <c r="G40" s="9" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -18687,18 +18701,18 @@
       <c r="B41" s="11" t="n"/>
       <c r="C41" s="11" t="n"/>
       <c r="D41" s="12" t="n"/>
-      <c r="E41" s="10">
+      <c r="E41" s="15">
         <f>SUM(E16:E40)</f>
         <v/>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="15">
         <f>SUM(F16:F40)</f>
         <v/>
       </c>
       <c r="G41" s="13" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -18707,7 +18721,7 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="10">
+      <c r="F42" s="15">
         <f>F41/E41*100</f>
         <v/>
       </c>
@@ -18715,7 +18729,7 @@
     </row>
     <row r="43" ht="9.75" customHeight="1"/>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -18724,11 +18738,11 @@
       <c r="C44" s="11" t="n"/>
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="12" t="n"/>
-      <c r="F44" s="10">
+      <c r="F44" s="15">
         <f>F42*30/100</f>
         <v/>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="G44" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -18895,7 +18909,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -18919,7 +18933,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -18943,7 +18957,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -18967,7 +18981,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -18992,7 +19006,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -19017,7 +19031,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -19045,7 +19059,7 @@
       </c>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -19073,7 +19087,7 @@
       </c>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -19101,7 +19115,7 @@
       </c>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -19125,7 +19139,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -19149,7 +19163,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -19173,7 +19187,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -19181,18 +19195,18 @@
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="12" t="n"/>
-      <c r="E27" s="10">
+      <c r="E27" s="15">
         <f>SUM(E16:E26)</f>
         <v/>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="15">
         <f>SUM(F16:F26)</f>
         <v/>
       </c>
       <c r="G27" s="13" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -19201,7 +19215,7 @@
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
+      <c r="F28" s="15">
         <f>F27/E27*100</f>
         <v/>
       </c>
@@ -19209,7 +19223,7 @@
     </row>
     <row r="29" ht="9.75" customHeight="1"/>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -19218,11 +19232,11 @@
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10">
+      <c r="F30" s="15">
         <f>F28*30/100</f>
         <v/>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -19387,7 +19401,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -19411,7 +19425,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -19435,7 +19449,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -19459,7 +19473,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -19483,7 +19497,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -19507,7 +19521,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -19531,7 +19545,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -19555,7 +19569,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -19579,7 +19593,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -19603,7 +19617,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -19611,18 +19625,18 @@
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="10">
+      <c r="E25" s="15">
         <f>SUM(E16:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="15">
         <f>SUM(F16:F24)</f>
         <v/>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -19631,7 +19645,7 @@
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="12" t="n"/>
-      <c r="F26" s="10">
+      <c r="F26" s="15">
         <f>F25/E25*100</f>
         <v/>
       </c>
@@ -19639,7 +19653,7 @@
     </row>
     <row r="27" ht="9.75" customHeight="1"/>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -19648,11 +19662,11 @@
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
+      <c r="F28" s="15">
         <f>F26*30/100</f>
         <v/>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -19817,7 +19831,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -19841,7 +19855,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -19865,7 +19879,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -19889,7 +19903,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -19913,7 +19927,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -19937,7 +19951,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -19961,7 +19975,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -19985,7 +19999,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -20009,7 +20023,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -20033,7 +20047,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -20057,7 +20071,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -20081,7 +20095,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -20105,7 +20119,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -20113,18 +20127,18 @@
       <c r="B28" s="11" t="n"/>
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="12" t="n"/>
-      <c r="E28" s="10">
+      <c r="E28" s="15">
         <f>SUM(E16:E27)</f>
         <v/>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="15">
         <f>SUM(F16:F27)</f>
         <v/>
       </c>
       <c r="G28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -20133,7 +20147,7 @@
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="11" t="n"/>
       <c r="E29" s="12" t="n"/>
-      <c r="F29" s="10">
+      <c r="F29" s="15">
         <f>F28/E28*100</f>
         <v/>
       </c>
@@ -20141,7 +20155,7 @@
     </row>
     <row r="30" ht="9.75" customHeight="1"/>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -20150,11 +20164,11 @@
       <c r="C31" s="11" t="n"/>
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="12" t="n"/>
-      <c r="F31" s="10">
+      <c r="F31" s="15">
         <f>F29*30/100</f>
         <v/>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -20321,7 +20335,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -20345,7 +20359,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -20369,7 +20383,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -20393,7 +20407,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -20417,7 +20431,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -20441,7 +20455,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -20465,7 +20479,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -20489,7 +20503,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -20513,7 +20527,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -20537,7 +20551,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -20561,7 +20575,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -20585,7 +20599,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -20593,18 +20607,18 @@
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="12" t="n"/>
-      <c r="E27" s="10">
+      <c r="E27" s="15">
         <f>SUM(E16:E26)</f>
         <v/>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="15">
         <f>SUM(F16:F26)</f>
         <v/>
       </c>
       <c r="G27" s="13" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -20613,7 +20627,7 @@
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
+      <c r="F28" s="15">
         <f>F27/E27*100</f>
         <v/>
       </c>
@@ -20621,7 +20635,7 @@
     </row>
     <row r="29" ht="9.75" customHeight="1"/>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -20630,11 +20644,11 @@
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10">
+      <c r="F30" s="15">
         <f>F28*30/100</f>
         <v/>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>

--- a/lab-standards/BMET-lab-standard.xlsx
+++ b/lab-standards/BMET-lab-standard.xlsx
@@ -8718,7 +8718,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
 (Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>

--- a/lab-standards/BMET-lab-standard.xlsx
+++ b/lab-standards/BMET-lab-standard.xlsx
@@ -8586,7 +8586,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -8609,7 +8608,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -8652,8 +8650,6 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -8661,7 +8657,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -8673,7 +8668,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -12012,7 +12006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -12590,9 +12584,17 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="14.15" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the institute should have at least 8 welding booths. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A1:G1"/>

--- a/lab-standards/BMET-lab-standard.xlsx
+++ b/lab-standards/BMET-lab-standard.xlsx
@@ -13793,7 +13793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -14539,13 +14539,21 @@
         </is>
       </c>
     </row>
+    <row r="43" ht="28.3" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the institute should have at least 15 channel wiring boards/booths and 3 concealed wiring booths. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A40:E40"/>
